--- a/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_march_2026_receipts.xlsx
+++ b/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_march_2026_receipts.xlsx
@@ -18,6 +18,7 @@
     <ns0:sheet name="3.2" sheetId="194" ns7:id="rId3"/>
     <ns0:sheet name="3.7" sheetId="204" ns7:id="rId8"/>
     <ns0:sheet name="3.8" sheetId="192" ns7:id="rId9"/>
+    <ns0:sheet name="3.10" sheetId="261" ns7:id="rId11"/>
   </ns0:sheets>
   <ns0:definedNames>
     <ns0:definedName name="________tab3" localSheetId="18">!#REF!</ns0:definedName>
@@ -4045,6 +4046,287 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{270C67AD-4C14-4065-AB23-9509227752CC}">
+  <sheetPr codeName="Sheet30">
+    <tabColor theme="4" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="354" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" style="354" customWidth="1"/>
+    <col min="3" max="8" width="10" style="354" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="354"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="339" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" thickBot="1">
+      <c r="B2" s="563" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="564"/>
+      <c r="D2" s="564"/>
+      <c r="E2" s="564"/>
+      <c r="F2" s="564"/>
+      <c r="G2" s="564"/>
+      <c r="H2" s="565"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" s="343"/>
+      <c r="C3" s="561" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="561"/>
+      <c r="E3" s="561"/>
+      <c r="F3" s="561"/>
+      <c r="G3" s="561"/>
+      <c r="H3" s="562"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="269"/>
+      <c r="C4" s="559" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="559"/>
+      <c r="E4" s="559"/>
+      <c r="F4" s="559"/>
+      <c r="G4" s="559"/>
+      <c r="H4" s="560"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="269"/>
+      <c r="C5" s="264" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="264" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="264" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="264" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="264" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="340" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B6" s="272" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="356">
+        <v>3.7972275673045832</v>
+      </c>
+      <c r="D6" s="356">
+        <v>4.7977750909717853</v>
+      </c>
+      <c r="E6" s="356">
+        <v>5.1562161360302587</v>
+      </c>
+      <c r="F6" s="356">
+        <v>5.3562538432896201</v>
+      </c>
+      <c r="G6" s="356">
+        <v>5.5388440890340274</v>
+      </c>
+      <c r="H6" s="357">
+        <v>5.6840393787403398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B7" s="273" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="265"/>
+      <c r="D7" s="265"/>
+      <c r="E7" s="265"/>
+      <c r="F7" s="265"/>
+      <c r="G7" s="265"/>
+      <c r="H7" s="267"/>
+    </row>
+    <row r="8" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B8" s="276" t="s">
+        <v>253</v>
+      </c>
+      <c r="C8" s="265">
+        <v>1.312896340550628</v>
+      </c>
+      <c r="D8" s="265">
+        <v>2.3161989343494422</v>
+      </c>
+      <c r="E8" s="265">
+        <v>2.4150072286414543</v>
+      </c>
+      <c r="F8" s="265">
+        <v>2.5371533459117006</v>
+      </c>
+      <c r="G8" s="265">
+        <v>2.6491836780604188</v>
+      </c>
+      <c r="H8" s="267">
+        <v>2.7306035741759453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B9" s="276" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="265">
+        <v>0.96112324524158754</v>
+      </c>
+      <c r="D9" s="265">
+        <v>1.0085681777616253</v>
+      </c>
+      <c r="E9" s="265">
+        <v>1.0341499168843902</v>
+      </c>
+      <c r="F9" s="265">
+        <v>1.0590432874187228</v>
+      </c>
+      <c r="G9" s="265">
+        <v>1.0900246600358603</v>
+      </c>
+      <c r="H9" s="267">
+        <v>1.1149544752961229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B10" s="276" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="265">
+        <v>0.6730606094724928</v>
+      </c>
+      <c r="D10" s="265">
+        <v>0.69778590690050302</v>
+      </c>
+      <c r="E10" s="265">
+        <v>0.92838385767587883</v>
+      </c>
+      <c r="F10" s="265">
+        <v>0.97136805940446491</v>
+      </c>
+      <c r="G10" s="265">
+        <v>1.0025732078128275</v>
+      </c>
+      <c r="H10" s="267">
+        <v>1.0340445095421</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B11" s="276" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="265">
+        <v>0.62861473757399211</v>
+      </c>
+      <c r="D11" s="265">
+        <v>0.60942497205580215</v>
+      </c>
+      <c r="E11" s="265">
+        <v>0.61520645642337479</v>
+      </c>
+      <c r="F11" s="265">
+        <v>0.62456887662211369</v>
+      </c>
+      <c r="G11" s="265">
+        <v>0.63433996958674899</v>
+      </c>
+      <c r="H11" s="267">
+        <v>0.64884821213584543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B12" s="276" t="s">
+        <v>255</v>
+      </c>
+      <c r="C12" s="265">
+        <v>0.19430257515489857</v>
+      </c>
+      <c r="D12" s="265">
+        <v>0.16152282987590175</v>
+      </c>
+      <c r="E12" s="265">
+        <v>0.15895769101927501</v>
+      </c>
+      <c r="F12" s="265">
+        <v>0.15957236791081084</v>
+      </c>
+      <c r="G12" s="265">
+        <v>0.15798637304398647</v>
+      </c>
+      <c r="H12" s="267">
+        <v>0.15076269408490447</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="13.5" customHeight="1">
+      <c r="B13" s="276" t="s">
+        <v>256</v>
+      </c>
+      <c r="C13" s="265">
+        <v>2.3468950845847075E-2</v>
+      </c>
+      <c r="D13" s="265">
+        <v>1.3709635323819284E-8</v>
+      </c>
+      <c r="E13" s="265">
+        <v>3.7090695150306794E-8</v>
+      </c>
+      <c r="F13" s="265">
+        <v>3.8199404950839866E-8</v>
+      </c>
+      <c r="G13" s="265">
+        <v>3.8960655399193704E-8</v>
+      </c>
+      <c r="H13" s="267">
+        <v>4.0149031057811823E-8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B14" s="277" t="s">
+        <v>257</v>
+      </c>
+      <c r="C14" s="341">
+        <v>3.7611084651374858E-3</v>
+      </c>
+      <c r="D14" s="341">
+        <v>4.2742563188752965E-3</v>
+      </c>
+      <c r="E14" s="341">
+        <v>4.5109482951906227E-3</v>
+      </c>
+      <c r="F14" s="341">
+        <v>4.547867822402683E-3</v>
+      </c>
+      <c r="G14" s="341">
+        <v>4.7361615335291072E-3</v>
+      </c>
+      <c r="H14" s="342">
+        <v>4.825873356391056E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{8326E600-4ACE-4B09-A201-6586B1299CBB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657582D5-BD3B-4482-82A3-154823C755A5}">
   <sheetPr codeName="Sheet4">

--- a/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_march_2026_receipts.xlsx
+++ b/policyengine_uk/tests/fixtures/obr_receipts/obr_efo_march_2026_receipts.xlsx
@@ -19,6 +19,8 @@
     <ns0:sheet name="3.7" sheetId="204" ns7:id="rId8"/>
     <ns0:sheet name="3.8" sheetId="192" ns7:id="rId9"/>
     <ns0:sheet name="3.10" sheetId="261" ns7:id="rId11"/>
+    <ns0:sheet name="3.11" sheetId="208" ns7:id="rId12"/>
+    <ns0:sheet name="3.12" sheetId="209" ns7:id="rId13"/>
   </ns0:sheets>
   <ns0:definedNames>
     <ns0:definedName name="________tab3" localSheetId="18">!#REF!</ns0:definedName>
@@ -4327,6 +4329,606 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD633EC-985A-453A-B0BD-4801B0D465F1}">
+  <sheetPr codeName="Sheet13">
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" style="2" customWidth="1"/>
+    <col min="3" max="9" width="10" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.42578125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" thickBot="1">
+      <c r="B2" s="543" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="544"/>
+      <c r="D2" s="544"/>
+      <c r="E2" s="544"/>
+      <c r="F2" s="544"/>
+      <c r="G2" s="544"/>
+      <c r="H2" s="544"/>
+      <c r="I2" s="545"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B3" s="123"/>
+      <c r="C3" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="566" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="566"/>
+      <c r="F3" s="566"/>
+      <c r="G3" s="566"/>
+      <c r="H3" s="566"/>
+      <c r="I3" s="567"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="124"/>
+      <c r="C4" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B5" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="126">
+        <v>13578.199084269218</v>
+      </c>
+      <c r="D5" s="126">
+        <v>12254.443899171421</v>
+      </c>
+      <c r="E5" s="126">
+        <v>10935.71615536125</v>
+      </c>
+      <c r="F5" s="126">
+        <v>9796.6640404179016</v>
+      </c>
+      <c r="G5" s="126">
+        <v>8866.6130178015883</v>
+      </c>
+      <c r="H5" s="126">
+        <v>7995.729597841897</v>
+      </c>
+      <c r="I5" s="127">
+        <v>7564.6566739628925</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B6" s="128" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="126">
+        <v>4725.0674729508255</v>
+      </c>
+      <c r="D6" s="126">
+        <v>4195.6620273884218</v>
+      </c>
+      <c r="E6" s="126">
+        <v>3971.5085113661867</v>
+      </c>
+      <c r="F6" s="126">
+        <v>3475.5634851735645</v>
+      </c>
+      <c r="G6" s="126">
+        <v>3385.8348077623691</v>
+      </c>
+      <c r="H6" s="126">
+        <v>3220.9042106778179</v>
+      </c>
+      <c r="I6" s="127">
+        <v>3135.9703219984908</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B7" s="328" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="126"/>
+      <c r="I7" s="127"/>
+    </row>
+    <row r="8" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B8" s="129" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="126">
+        <v>4028.4786869103718</v>
+      </c>
+      <c r="D8" s="126">
+        <v>3526.3857151341385</v>
+      </c>
+      <c r="E8" s="126">
+        <v>3293.6576388022659</v>
+      </c>
+      <c r="F8" s="126">
+        <v>2892.1697163272493</v>
+      </c>
+      <c r="G8" s="126">
+        <v>2753.8285838812085</v>
+      </c>
+      <c r="H8" s="126">
+        <v>2585.2813720012768</v>
+      </c>
+      <c r="I8" s="127">
+        <v>2487.166773432516</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="13.5" customHeight="1" thickBot="1">
+      <c r="B9" s="130" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="131">
+        <v>696.58878604045401</v>
+      </c>
+      <c r="D9" s="131">
+        <v>669.27631225428354</v>
+      </c>
+      <c r="E9" s="131">
+        <v>677.85087256392069</v>
+      </c>
+      <c r="F9" s="131">
+        <v>583.39376884631531</v>
+      </c>
+      <c r="G9" s="131">
+        <v>632.00622388116062</v>
+      </c>
+      <c r="H9" s="131">
+        <v>635.62283867654082</v>
+      </c>
+      <c r="I9" s="132">
+        <v>648.80354856597478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10" s="51"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
+      <c r="I10" s="126"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D3:I3"/>
+  </mergeCells>
+  <phoneticPr fontId="41" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{F640A598-9E5A-4835-9386-045783020007}"/>
+  </hyperlinks>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3957F9A-7C4D-409C-A28F-BE8B87961F74}">
+  <sheetPr codeName="Sheet14">
+    <tabColor theme="6"/>
+  </sheetPr>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="2" customWidth="1"/>
+    <col min="4" max="9" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.42578125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="33.75" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" thickBot="1">
+      <c r="B2" s="577" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="578"/>
+      <c r="D2" s="578"/>
+      <c r="E2" s="578"/>
+      <c r="F2" s="578"/>
+      <c r="G2" s="578"/>
+      <c r="H2" s="578"/>
+      <c r="I2" s="579"/>
+    </row>
+    <row r="3" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B3" s="133"/>
+      <c r="C3" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="536" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="536"/>
+      <c r="F3" s="536"/>
+      <c r="G3" s="536"/>
+      <c r="H3" s="536"/>
+      <c r="I3" s="537"/>
+    </row>
+    <row r="4" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B4" s="134"/>
+      <c r="C4" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B5" s="329" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="135">
+        <v>2168.2921615793966</v>
+      </c>
+      <c r="D5" s="135">
+        <v>2083.3332688432952</v>
+      </c>
+      <c r="E5" s="135">
+        <v>2047.9991564911497</v>
+      </c>
+      <c r="F5" s="135">
+        <v>2055.0663286925724</v>
+      </c>
+      <c r="G5" s="135">
+        <v>2069.6074004097741</v>
+      </c>
+      <c r="H5" s="135">
+        <v>2085.2376704507528</v>
+      </c>
+      <c r="I5" s="136">
+        <v>2101.0702511760765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B6" s="329" t="s">
+        <v>228</v>
+      </c>
+      <c r="C6" s="135">
+        <v>1619.9398031719702</v>
+      </c>
+      <c r="D6" s="135">
+        <v>1534.8113403538073</v>
+      </c>
+      <c r="E6" s="135">
+        <v>1521.0993234521127</v>
+      </c>
+      <c r="F6" s="135">
+        <v>1529.4264001780152</v>
+      </c>
+      <c r="G6" s="135">
+        <v>1542.2932290667245</v>
+      </c>
+      <c r="H6" s="135">
+        <v>1555.708517982323</v>
+      </c>
+      <c r="I6" s="136">
+        <v>1569.3328887285095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B7" s="185" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="137">
+        <v>1289.5543778979199</v>
+      </c>
+      <c r="D7" s="137">
+        <v>1239.4917691306655</v>
+      </c>
+      <c r="E7" s="137">
+        <v>1236.8062704924209</v>
+      </c>
+      <c r="F7" s="137">
+        <v>1240.0908662025893</v>
+      </c>
+      <c r="G7" s="137">
+        <v>1247.2437066467319</v>
+      </c>
+      <c r="H7" s="137">
+        <v>1254.8362045261438</v>
+      </c>
+      <c r="I7" s="138">
+        <v>1262.8339376703782</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="12" customHeight="1">
+      <c r="B8" s="571" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" s="580"/>
+      <c r="D8" s="580"/>
+      <c r="E8" s="580"/>
+      <c r="F8" s="580"/>
+      <c r="G8" s="580"/>
+      <c r="H8" s="580"/>
+      <c r="I8" s="581"/>
+    </row>
+    <row r="9" spans="1:9" ht="12" customHeight="1">
+      <c r="B9" s="568" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="569"/>
+      <c r="D9" s="569"/>
+      <c r="E9" s="569"/>
+      <c r="F9" s="569"/>
+      <c r="G9" s="569"/>
+      <c r="H9" s="569"/>
+      <c r="I9" s="570"/>
+    </row>
+    <row r="10" spans="1:9" ht="12" customHeight="1" thickBot="1">
+      <c r="B10" s="574" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="575"/>
+      <c r="D10" s="575"/>
+      <c r="E10" s="575"/>
+      <c r="F10" s="575"/>
+      <c r="G10" s="575"/>
+      <c r="H10" s="575"/>
+      <c r="I10" s="576"/>
+    </row>
+    <row r="11" spans="1:9" ht="13.5" thickBot="1"/>
+    <row r="12" spans="1:9" ht="18" customHeight="1" thickBot="1">
+      <c r="B12" s="577" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="578"/>
+      <c r="D12" s="578"/>
+      <c r="E12" s="578"/>
+      <c r="F12" s="578"/>
+      <c r="G12" s="578"/>
+      <c r="H12" s="578"/>
+      <c r="I12" s="579"/>
+    </row>
+    <row r="13" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B13" s="139"/>
+      <c r="C13" s="582" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="582"/>
+      <c r="E13" s="582"/>
+      <c r="F13" s="582"/>
+      <c r="G13" s="582"/>
+      <c r="H13" s="582"/>
+      <c r="I13" s="583"/>
+    </row>
+    <row r="14" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B14" s="133"/>
+      <c r="C14" s="85" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="584" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="584"/>
+      <c r="F14" s="584"/>
+      <c r="G14" s="584"/>
+      <c r="H14" s="584"/>
+      <c r="I14" s="585"/>
+    </row>
+    <row r="15" spans="1:9" ht="12.75" customHeight="1">
+      <c r="B15" s="134"/>
+      <c r="C15" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I15" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B16" s="329" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="140">
+        <v>3.746</v>
+      </c>
+      <c r="D16" s="140">
+        <v>3.7522180684197259</v>
+      </c>
+      <c r="E16" s="140">
+        <v>3.880151089723141</v>
+      </c>
+      <c r="F16" s="140">
+        <v>4.018176993807419</v>
+      </c>
+      <c r="G16" s="140">
+        <v>4.1693079340231609</v>
+      </c>
+      <c r="H16" s="140">
+        <v>4.3250673466154277</v>
+      </c>
+      <c r="I16" s="141">
+        <v>4.4602881111325283</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="13.5" customHeight="1">
+      <c r="B17" s="329" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="140">
+        <v>4.6859999999999999</v>
+      </c>
+      <c r="D17" s="140">
+        <v>4.5219801471629513</v>
+      </c>
+      <c r="E17" s="140">
+        <v>4.6669613483522516</v>
+      </c>
+      <c r="F17" s="140">
+        <v>4.8302825927639859</v>
+      </c>
+      <c r="G17" s="140">
+        <v>5.0116066487673416</v>
+      </c>
+      <c r="H17" s="140">
+        <v>5.1921078579978026</v>
+      </c>
+      <c r="I17" s="141">
+        <v>5.3512903316491176</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="13.5" customHeight="1">
+      <c r="B18" s="329" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="140">
+        <v>4.1130000000000004</v>
+      </c>
+      <c r="D18" s="140">
+        <v>4.0226946799375609</v>
+      </c>
+      <c r="E18" s="140">
+        <v>4.1387829957037807</v>
+      </c>
+      <c r="F18" s="140">
+        <v>4.2728836001298376</v>
+      </c>
+      <c r="G18" s="140">
+        <v>4.42503354926024</v>
+      </c>
+      <c r="H18" s="140">
+        <v>4.5748019900340235</v>
+      </c>
+      <c r="I18" s="142">
+        <v>4.7067726858720214</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="12" customHeight="1">
+      <c r="B19" s="571" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="572"/>
+      <c r="D19" s="572"/>
+      <c r="E19" s="572"/>
+      <c r="F19" s="572"/>
+      <c r="G19" s="572"/>
+      <c r="H19" s="572"/>
+      <c r="I19" s="573"/>
+    </row>
+    <row r="20" spans="2:9" ht="12" customHeight="1">
+      <c r="B20" s="568" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="569"/>
+      <c r="D20" s="569"/>
+      <c r="E20" s="569"/>
+      <c r="F20" s="569"/>
+      <c r="G20" s="569"/>
+      <c r="H20" s="569"/>
+      <c r="I20" s="570"/>
+    </row>
+    <row r="21" spans="2:9" ht="12" customHeight="1" thickBot="1">
+      <c r="B21" s="574" t="s">
+        <v>238</v>
+      </c>
+      <c r="C21" s="575"/>
+      <c r="D21" s="575"/>
+      <c r="E21" s="575"/>
+      <c r="F21" s="575"/>
+      <c r="G21" s="575"/>
+      <c r="H21" s="575"/>
+      <c r="I21" s="576"/>
+    </row>
+    <row r="24" spans="2:9" ht="19.350000000000001" customHeight="1"/>
+    <row r="25" spans="2:9" ht="19.350000000000001" customHeight="1"/>
+    <row r="34" s="2" customFormat="1" ht="18.600000000000001" customHeight="1"/>
+    <row r="35" s="2" customFormat="1" ht="19.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="D14:I14"/>
+  </mergeCells>
+  <phoneticPr fontId="41" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Contents!A1" display="Back to contents" xr:uid="{9FA62B33-BAC6-4FD9-A12D-4178AF2CE126}"/>
+  </hyperlinks>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657582D5-BD3B-4482-82A3-154823C755A5}">
   <sheetPr codeName="Sheet4">
